--- a/backend/src/main/resources/plan-curricular-plantilla.xlsx
+++ b/backend/src/main/resources/plan-curricular-plantilla.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abril" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mayo" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Junio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Julio" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -806,14 +807,14 @@
   </twoCellAnchor>
   <twoCellAnchor editAs="oneCell">
     <from>
-      <col>25</col>
-      <colOff>267773</colOff>
+      <col>24</col>
+      <colOff>479439</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
     <to>
-      <col>37</col>
-      <colOff>183797</colOff>
+      <col>35</col>
+      <colOff>1386416</colOff>
       <row>3</row>
       <rowOff>166680</rowOff>
     </to>
@@ -831,8 +832,8 @@
       </blipFill>
       <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="9221273" y="0"/>
-          <a:ext cx="3916524" cy="844013"/>
+          <a:off x="8946106" y="0"/>
+          <a:ext cx="3669227" cy="844013"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -865,7 +866,7 @@
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Imagen 2"/>
+        <cNvPr id="2" name="Imagen 2"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -877,7 +878,7 @@
       <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1323360" y="0"/>
-          <a:ext cx="659880" cy="776520"/>
+          <a:ext cx="659880" cy="791640"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -892,20 +893,20 @@
   </twoCellAnchor>
   <twoCellAnchor editAs="oneCell">
     <from>
-      <col>25</col>
-      <colOff>341856</colOff>
+      <col>24</col>
+      <colOff>479439</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
     <to>
-      <col>37</col>
-      <colOff>257880</colOff>
-      <row>4</row>
-      <rowOff>6480</rowOff>
+      <col>35</col>
+      <colOff>1386416</colOff>
+      <row>3</row>
+      <rowOff>166680</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Imagen 4"/>
+        <cNvPr id="3" name="Imagen 4"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -917,8 +918,8 @@
       </blipFill>
       <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="9295356" y="0"/>
-          <a:ext cx="3916524" cy="831980"/>
+          <a:off x="8946106" y="0"/>
+          <a:ext cx="3669227" cy="844013"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -951,7 +952,7 @@
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Imagen 2"/>
+        <cNvPr id="2" name="Imagen 2"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -963,7 +964,7 @@
       <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1323360" y="0"/>
-          <a:ext cx="659880" cy="776520"/>
+          <a:ext cx="659880" cy="791640"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -978,20 +979,20 @@
   </twoCellAnchor>
   <twoCellAnchor editAs="oneCell">
     <from>
-      <col>25</col>
-      <colOff>481227</colOff>
+      <col>24</col>
+      <colOff>479439</colOff>
       <row>0</row>
-      <rowOff>74084</rowOff>
+      <rowOff>0</rowOff>
     </from>
     <to>
       <col>35</col>
-      <colOff>1358547</colOff>
+      <colOff>1386416</colOff>
       <row>3</row>
-      <rowOff>96764</rowOff>
+      <rowOff>166680</rowOff>
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Imagen 4"/>
+        <cNvPr id="3" name="Imagen 4"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -1003,8 +1004,94 @@
       </blipFill>
       <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="9434727" y="74084"/>
-          <a:ext cx="3152737" cy="668263"/>
+          <a:off x="8946106" y="0"/>
+          <a:ext cx="3669227" cy="844013"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>54720</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>5</col>
+      <colOff>29880</colOff>
+      <row>3</row>
+      <rowOff>160560</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="1323360" y="0"/>
+          <a:ext cx="659880" cy="791640"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>24</col>
+      <colOff>479439</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>35</col>
+      <colOff>1386416</colOff>
+      <row>3</row>
+      <rowOff>166680</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Imagen 4"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5417" t="3475" r="-1514" b="90112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="8946106" y="0"/>
+          <a:ext cx="3669227" cy="844013"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -1236,14 +1323,14 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="59" t="inlineStr">
         <is>
-          <t>2. Por cada mes, cargá hasta 4 bloques temáticos con: Capacidades, Temas/Contenidos, Actividades, Instrumentos de evaluación e Indicadores (Conceptual, Procedimental, Actitudinal).</t>
+          <t>2. Por cada mes, completá los bloques temáticos con: Capacidades, Temas/Contenidos, Actividades, Instrumentos de evaluación e Indicadores (Conceptual, Procedimental, Actitudinal).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="59" t="inlineStr">
         <is>
-          <t>3. La hoja "Marzo" ya trae el primer bloque como ejemplo de referencia — no lo dejes así, reemplazalo por tu propio contenido.</t>
+          <t>3. La cantidad de meses y de bloques por mes ya viene armada según la configuración elegida al descargar la plantilla.</t>
         </is>
       </c>
     </row>
@@ -5805,4 +5892,1148 @@
   <pageSetup orientation="landscape" paperSize="5" scale="70" horizontalDpi="300" verticalDpi="300"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:AJ52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.85546875" customWidth="1" min="1" max="1"/>
+    <col width="9.28515625" customWidth="1" min="2" max="2"/>
+    <col width="4.85546875" customWidth="1" min="3" max="6"/>
+    <col width="3.7109375" customWidth="1" min="7" max="17"/>
+    <col width="3.7109375" customWidth="1" style="2" min="18" max="18"/>
+    <col width="7.85546875" customWidth="1" min="19" max="19"/>
+    <col width="13.140625" customWidth="1" min="20" max="20"/>
+    <col width="7.28515625" customWidth="1" min="21" max="26"/>
+    <col hidden="1" width="7.28515625" customWidth="1" min="27" max="27"/>
+    <col width="5.7109375" customWidth="1" min="28" max="30"/>
+    <col width="2.85546875" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="5.7109375" customWidth="1" min="32" max="34"/>
+    <col width="6.85546875" customWidth="1" min="35" max="35"/>
+    <col width="21" customWidth="1" min="36" max="36"/>
+    <col width="4.85546875" customWidth="1" min="37" max="37"/>
+    <col width="11.5703125" customWidth="1" min="16384" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="C2" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MINISTERIO DE EDUCACIÓN Y CIENCIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="C3" s="44" t="inlineStr">
+        <is>
+          <t>COLEGIO TÉCNICO NACIONAL DE ASUNCIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="31" t="n"/>
+      <c r="D4" s="61" t="n"/>
+      <c r="E4" s="61" t="n"/>
+      <c r="F4" s="61" t="n"/>
+      <c r="G4" s="61" t="n"/>
+      <c r="H4" s="61" t="n"/>
+      <c r="I4" s="61" t="n"/>
+      <c r="J4" s="61" t="n"/>
+      <c r="K4" s="61" t="n"/>
+      <c r="L4" s="61" t="n"/>
+      <c r="M4" s="61" t="n"/>
+      <c r="N4" s="61" t="n"/>
+      <c r="O4" s="61" t="n"/>
+      <c r="P4" s="61" t="n"/>
+      <c r="Q4" s="61" t="n"/>
+      <c r="R4" s="61" t="n"/>
+      <c r="S4" s="61" t="n"/>
+      <c r="T4" s="61" t="n"/>
+      <c r="U4" s="61" t="n"/>
+      <c r="V4" s="61" t="n"/>
+      <c r="W4" s="61" t="n"/>
+      <c r="X4" s="61" t="n"/>
+      <c r="Y4" s="61" t="n"/>
+      <c r="Z4" s="61" t="n"/>
+      <c r="AA4" s="61" t="n"/>
+      <c r="AB4" s="61" t="n"/>
+      <c r="AC4" s="61" t="n"/>
+      <c r="AD4" s="61" t="n"/>
+      <c r="AE4" s="61" t="n"/>
+      <c r="AF4" s="61" t="n"/>
+      <c r="AG4" s="61" t="n"/>
+      <c r="AH4" s="61" t="n"/>
+      <c r="AI4" s="61" t="n"/>
+      <c r="AJ4" s="61" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="B5" s="62" t="n"/>
+      <c r="C5" s="63" t="n"/>
+      <c r="D5" s="63" t="n"/>
+      <c r="E5" s="63" t="n"/>
+      <c r="F5" s="63" t="n"/>
+      <c r="G5" s="63" t="n"/>
+      <c r="H5" s="63" t="n"/>
+      <c r="I5" s="63" t="n"/>
+      <c r="J5" s="63" t="n"/>
+      <c r="K5" s="63" t="n"/>
+      <c r="L5" s="63" t="n"/>
+      <c r="M5" s="63" t="n"/>
+      <c r="N5" s="63" t="n"/>
+      <c r="O5" s="63" t="n"/>
+      <c r="P5" s="63" t="n"/>
+      <c r="Q5" s="63" t="n"/>
+      <c r="R5" s="63" t="n"/>
+      <c r="S5" s="63" t="n"/>
+      <c r="T5" s="63" t="n"/>
+      <c r="U5" s="63" t="n"/>
+      <c r="V5" s="63" t="n"/>
+      <c r="W5" s="63" t="n"/>
+      <c r="X5" s="63" t="n"/>
+      <c r="Y5" s="63" t="n"/>
+      <c r="Z5" s="63" t="n"/>
+      <c r="AA5" s="63" t="n"/>
+      <c r="AB5" s="63" t="n"/>
+      <c r="AC5" s="63" t="n"/>
+      <c r="AD5" s="63" t="n"/>
+      <c r="AE5" s="63" t="n"/>
+      <c r="AF5" s="63" t="n"/>
+      <c r="AG5" s="63" t="n"/>
+      <c r="AH5" s="63" t="n"/>
+      <c r="AI5" s="63" t="n"/>
+      <c r="AJ5" s="64" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="B6" s="65" t="n"/>
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="61" t="n"/>
+      <c r="E6" s="61" t="n"/>
+      <c r="F6" s="61" t="n"/>
+      <c r="G6" s="61" t="n"/>
+      <c r="H6" s="61" t="n"/>
+      <c r="I6" s="61" t="n"/>
+      <c r="J6" s="61" t="n"/>
+      <c r="K6" s="61" t="n"/>
+      <c r="L6" s="61" t="n"/>
+      <c r="M6" s="61" t="n"/>
+      <c r="N6" s="61" t="n"/>
+      <c r="O6" s="61" t="n"/>
+      <c r="P6" s="61" t="n"/>
+      <c r="Q6" s="61" t="n"/>
+      <c r="R6" s="61" t="n"/>
+      <c r="S6" s="61" t="n"/>
+      <c r="T6" s="61" t="n"/>
+      <c r="U6" s="61" t="n"/>
+      <c r="V6" s="61" t="n"/>
+      <c r="W6" s="61" t="n"/>
+      <c r="X6" s="61" t="n"/>
+      <c r="Y6" s="61" t="n"/>
+      <c r="Z6" s="61" t="n"/>
+      <c r="AA6" s="61" t="n"/>
+      <c r="AB6" s="61" t="n"/>
+      <c r="AC6" s="61" t="n"/>
+      <c r="AD6" s="61" t="n"/>
+      <c r="AE6" s="61" t="n"/>
+      <c r="AF6" s="61" t="n"/>
+      <c r="AG6" s="61" t="n"/>
+      <c r="AH6" s="61" t="n"/>
+      <c r="AI6" s="61" t="n"/>
+      <c r="AJ6" s="66" t="n"/>
+    </row>
+    <row r="7" ht="24.75" customHeight="1">
+      <c r="B7" s="67" t="n"/>
+      <c r="C7" s="63" t="n"/>
+      <c r="D7" s="63" t="n"/>
+      <c r="E7" s="63" t="n"/>
+      <c r="F7" s="63" t="n"/>
+      <c r="G7" s="63" t="n"/>
+      <c r="H7" s="63" t="n"/>
+      <c r="I7" s="63" t="n"/>
+      <c r="J7" s="63" t="n"/>
+      <c r="K7" s="63" t="n"/>
+      <c r="L7" s="63" t="n"/>
+      <c r="M7" s="63" t="n"/>
+      <c r="N7" s="63" t="n"/>
+      <c r="O7" s="63" t="n"/>
+      <c r="P7" s="63" t="n"/>
+      <c r="Q7" s="63" t="n"/>
+      <c r="R7" s="63" t="n"/>
+      <c r="S7" s="63" t="n"/>
+      <c r="T7" s="63" t="n"/>
+      <c r="U7" s="63" t="n"/>
+      <c r="V7" s="64" t="n"/>
+      <c r="W7" s="68" t="n"/>
+      <c r="X7" s="63" t="n"/>
+      <c r="Y7" s="63" t="n"/>
+      <c r="Z7" s="63" t="n"/>
+      <c r="AA7" s="63" t="n"/>
+      <c r="AB7" s="63" t="n"/>
+      <c r="AC7" s="63" t="n"/>
+      <c r="AD7" s="63" t="n"/>
+      <c r="AE7" s="63" t="n"/>
+      <c r="AF7" s="63" t="n"/>
+      <c r="AG7" s="63" t="n"/>
+      <c r="AH7" s="63" t="n"/>
+      <c r="AI7" s="63" t="n"/>
+      <c r="AJ7" s="64" t="n"/>
+    </row>
+    <row r="8" ht="24.75" customHeight="1">
+      <c r="B8" s="65" t="n"/>
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="61" t="n"/>
+      <c r="E8" s="61" t="n"/>
+      <c r="F8" s="61" t="n"/>
+      <c r="G8" s="61" t="n"/>
+      <c r="H8" s="61" t="n"/>
+      <c r="I8" s="61" t="n"/>
+      <c r="J8" s="61" t="n"/>
+      <c r="K8" s="61" t="n"/>
+      <c r="L8" s="61" t="n"/>
+      <c r="M8" s="61" t="n"/>
+      <c r="N8" s="61" t="n"/>
+      <c r="O8" s="61" t="n"/>
+      <c r="P8" s="61" t="n"/>
+      <c r="Q8" s="61" t="n"/>
+      <c r="R8" s="61" t="n"/>
+      <c r="S8" s="61" t="n"/>
+      <c r="T8" s="61" t="n"/>
+      <c r="U8" s="61" t="n"/>
+      <c r="V8" s="66" t="n"/>
+      <c r="W8" s="65" t="n"/>
+      <c r="X8" s="61" t="n"/>
+      <c r="Y8" s="61" t="n"/>
+      <c r="Z8" s="61" t="n"/>
+      <c r="AA8" s="61" t="n"/>
+      <c r="AB8" s="61" t="n"/>
+      <c r="AC8" s="61" t="n"/>
+      <c r="AD8" s="61" t="n"/>
+      <c r="AE8" s="61" t="n"/>
+      <c r="AF8" s="61" t="n"/>
+      <c r="AG8" s="61" t="n"/>
+      <c r="AH8" s="61" t="n"/>
+      <c r="AI8" s="61" t="n"/>
+      <c r="AJ8" s="66" t="n"/>
+    </row>
+    <row r="9" ht="24.75" customHeight="1">
+      <c r="B9" s="68" t="n"/>
+      <c r="C9" s="63" t="n"/>
+      <c r="D9" s="63" t="n"/>
+      <c r="E9" s="63" t="n"/>
+      <c r="F9" s="63" t="n"/>
+      <c r="G9" s="63" t="n"/>
+      <c r="H9" s="63" t="n"/>
+      <c r="I9" s="63" t="n"/>
+      <c r="J9" s="63" t="n"/>
+      <c r="K9" s="63" t="n"/>
+      <c r="L9" s="64" t="n"/>
+      <c r="M9" s="68" t="n"/>
+      <c r="N9" s="63" t="n"/>
+      <c r="O9" s="63" t="n"/>
+      <c r="P9" s="63" t="n"/>
+      <c r="Q9" s="63" t="n"/>
+      <c r="R9" s="64" t="n"/>
+      <c r="S9" s="68" t="n"/>
+      <c r="T9" s="63" t="n"/>
+      <c r="U9" s="63" t="n"/>
+      <c r="V9" s="64" t="n"/>
+      <c r="W9" s="68" t="n"/>
+      <c r="X9" s="63" t="n"/>
+      <c r="Y9" s="63" t="n"/>
+      <c r="Z9" s="63" t="n"/>
+      <c r="AA9" s="63" t="n"/>
+      <c r="AB9" s="63" t="n"/>
+      <c r="AC9" s="63" t="n"/>
+      <c r="AD9" s="63" t="n"/>
+      <c r="AE9" s="63" t="n"/>
+      <c r="AF9" s="63" t="n"/>
+      <c r="AG9" s="63" t="n"/>
+      <c r="AH9" s="63" t="n"/>
+      <c r="AI9" s="63" t="n"/>
+      <c r="AJ9" s="64" t="n"/>
+    </row>
+    <row r="10" ht="24.75" customHeight="1">
+      <c r="B10" s="65" t="n"/>
+      <c r="C10" s="61" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="E10" s="61" t="n"/>
+      <c r="F10" s="61" t="n"/>
+      <c r="G10" s="61" t="n"/>
+      <c r="H10" s="61" t="n"/>
+      <c r="I10" s="61" t="n"/>
+      <c r="J10" s="61" t="n"/>
+      <c r="K10" s="61" t="n"/>
+      <c r="L10" s="66" t="n"/>
+      <c r="M10" s="65" t="n"/>
+      <c r="N10" s="61" t="n"/>
+      <c r="O10" s="61" t="n"/>
+      <c r="P10" s="61" t="n"/>
+      <c r="Q10" s="61" t="n"/>
+      <c r="R10" s="66" t="n"/>
+      <c r="S10" s="65" t="n"/>
+      <c r="T10" s="61" t="n"/>
+      <c r="U10" s="61" t="n"/>
+      <c r="V10" s="66" t="n"/>
+      <c r="W10" s="65" t="n"/>
+      <c r="X10" s="61" t="n"/>
+      <c r="Y10" s="61" t="n"/>
+      <c r="Z10" s="61" t="n"/>
+      <c r="AA10" s="61" t="n"/>
+      <c r="AB10" s="61" t="n"/>
+      <c r="AC10" s="61" t="n"/>
+      <c r="AD10" s="61" t="n"/>
+      <c r="AE10" s="61" t="n"/>
+      <c r="AF10" s="61" t="n"/>
+      <c r="AG10" s="61" t="n"/>
+      <c r="AH10" s="61" t="n"/>
+      <c r="AI10" s="61" t="n"/>
+      <c r="AJ10" s="66" t="n"/>
+    </row>
+    <row r="11" ht="12" customHeight="1">
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
+      <c r="AA11" s="3" t="n"/>
+      <c r="AB11" s="3" t="n"/>
+      <c r="AC11" s="3" t="n"/>
+      <c r="AD11" s="3" t="n"/>
+      <c r="AE11" s="3" t="n"/>
+      <c r="AF11" s="3" t="n"/>
+      <c r="AG11" s="3" t="n"/>
+      <c r="AH11" s="3" t="n"/>
+      <c r="AI11" s="3" t="n"/>
+      <c r="AJ11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="38.25" customHeight="1">
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>1ra. Etapa</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>Capacidades</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="n"/>
+      <c r="E12" s="63" t="n"/>
+      <c r="F12" s="63" t="n"/>
+      <c r="G12" s="63" t="n"/>
+      <c r="H12" s="63" t="n"/>
+      <c r="I12" s="63" t="n"/>
+      <c r="J12" s="63" t="n"/>
+      <c r="K12" s="64" t="n"/>
+      <c r="L12" s="41" t="inlineStr">
+        <is>
+          <t>TEMAS/S CONTENIDO/S</t>
+        </is>
+      </c>
+      <c r="M12" s="63" t="n"/>
+      <c r="N12" s="63" t="n"/>
+      <c r="O12" s="63" t="n"/>
+      <c r="P12" s="63" t="n"/>
+      <c r="Q12" s="63" t="n"/>
+      <c r="R12" s="64" t="n"/>
+      <c r="S12" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actividades </t>
+        </is>
+      </c>
+      <c r="T12" s="63" t="n"/>
+      <c r="U12" s="63" t="n"/>
+      <c r="V12" s="63" t="n"/>
+      <c r="W12" s="63" t="n"/>
+      <c r="X12" s="63" t="n"/>
+      <c r="Y12" s="63" t="n"/>
+      <c r="Z12" s="63" t="n"/>
+      <c r="AA12" s="64" t="n"/>
+      <c r="AB12" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluación </t>
+        </is>
+      </c>
+      <c r="AC12" s="63" t="n"/>
+      <c r="AD12" s="63" t="n"/>
+      <c r="AE12" s="63" t="n"/>
+      <c r="AF12" s="63" t="n"/>
+      <c r="AG12" s="63" t="n"/>
+      <c r="AH12" s="63" t="n"/>
+      <c r="AI12" s="63" t="n"/>
+      <c r="AJ12" s="64" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="B13" s="69" t="n"/>
+      <c r="C13" s="70" t="n"/>
+      <c r="K13" s="69" t="n"/>
+      <c r="L13" s="70" t="n"/>
+      <c r="R13" s="69" t="n"/>
+      <c r="S13" s="70" t="n"/>
+      <c r="AA13" s="69" t="n"/>
+      <c r="AB13" s="65" t="n"/>
+      <c r="AC13" s="61" t="n"/>
+      <c r="AD13" s="61" t="n"/>
+      <c r="AE13" s="61" t="n"/>
+      <c r="AF13" s="61" t="n"/>
+      <c r="AG13" s="61" t="n"/>
+      <c r="AH13" s="61" t="n"/>
+      <c r="AI13" s="61" t="n"/>
+      <c r="AJ13" s="66" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="B14" s="69" t="n"/>
+      <c r="C14" s="65" t="n"/>
+      <c r="D14" s="61" t="n"/>
+      <c r="E14" s="61" t="n"/>
+      <c r="F14" s="61" t="n"/>
+      <c r="G14" s="61" t="n"/>
+      <c r="H14" s="61" t="n"/>
+      <c r="I14" s="61" t="n"/>
+      <c r="J14" s="61" t="n"/>
+      <c r="K14" s="66" t="n"/>
+      <c r="L14" s="65" t="n"/>
+      <c r="M14" s="61" t="n"/>
+      <c r="N14" s="61" t="n"/>
+      <c r="O14" s="61" t="n"/>
+      <c r="P14" s="61" t="n"/>
+      <c r="Q14" s="61" t="n"/>
+      <c r="R14" s="66" t="n"/>
+      <c r="S14" s="65" t="n"/>
+      <c r="T14" s="61" t="n"/>
+      <c r="U14" s="61" t="n"/>
+      <c r="V14" s="61" t="n"/>
+      <c r="W14" s="61" t="n"/>
+      <c r="X14" s="61" t="n"/>
+      <c r="Y14" s="61" t="n"/>
+      <c r="Z14" s="61" t="n"/>
+      <c r="AA14" s="66" t="n"/>
+      <c r="AB14" s="41" t="inlineStr">
+        <is>
+          <t>Instrumentos</t>
+        </is>
+      </c>
+      <c r="AC14" s="71" t="n"/>
+      <c r="AD14" s="71" t="n"/>
+      <c r="AE14" s="72" t="n"/>
+      <c r="AF14" s="5" t="n"/>
+      <c r="AG14" s="5" t="n"/>
+      <c r="AH14" s="5" t="n"/>
+      <c r="AI14" s="41" t="inlineStr">
+        <is>
+          <t>Indicadores</t>
+        </is>
+      </c>
+      <c r="AJ14" s="72" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="B15" s="69" t="n"/>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>Utiliza adecuadamente etiquetas básicas de HTML como &lt;html&gt;, &lt;head&gt;, &lt;title&gt;, &lt;body&gt; y &lt;p&gt; para estructurar y presentar contenidos simples en una página web.</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="n"/>
+      <c r="E15" s="63" t="n"/>
+      <c r="F15" s="63" t="n"/>
+      <c r="G15" s="63" t="n"/>
+      <c r="H15" s="63" t="n"/>
+      <c r="I15" s="63" t="n"/>
+      <c r="J15" s="63" t="n"/>
+      <c r="K15" s="64" t="n"/>
+      <c r="L15" s="34" t="inlineStr">
+        <is>
+          <t>Etiquetas basicas, sintaxis, extension, guardar y ejecutar archivos.</t>
+        </is>
+      </c>
+      <c r="M15" s="63" t="n"/>
+      <c r="N15" s="63" t="n"/>
+      <c r="O15" s="63" t="n"/>
+      <c r="P15" s="63" t="n"/>
+      <c r="Q15" s="63" t="n"/>
+      <c r="R15" s="64" t="n"/>
+      <c r="S15" s="34" t="inlineStr">
+        <is>
+          <t>Conexión con la clase-indagacion de saberes-Presentación de contenidos. -Exposición Oral -Ejemplos -Ejercicios guiados -Caso práctico -Revision de trabajos-Pase de lista.</t>
+        </is>
+      </c>
+      <c r="T15" s="63" t="n"/>
+      <c r="U15" s="63" t="n"/>
+      <c r="V15" s="63" t="n"/>
+      <c r="W15" s="63" t="n"/>
+      <c r="X15" s="63" t="n"/>
+      <c r="Y15" s="63" t="n"/>
+      <c r="Z15" s="63" t="n"/>
+      <c r="AA15" s="64" t="n"/>
+      <c r="AB15" s="43" t="inlineStr">
+        <is>
+          <t>Proceso por trabajos en clase. Portafolio de evidencias</t>
+        </is>
+      </c>
+      <c r="AC15" s="63" t="n"/>
+      <c r="AD15" s="63" t="n"/>
+      <c r="AE15" s="63" t="n"/>
+      <c r="AF15" s="12" t="n"/>
+      <c r="AG15" s="12" t="n"/>
+      <c r="AH15" s="12" t="n"/>
+      <c r="AI15" s="36" t="inlineStr">
+        <is>
+          <t>Conceptual: Conoce las etiquetas básicas del lenguaje html</t>
+        </is>
+      </c>
+      <c r="AJ15" s="64" t="n"/>
+    </row>
+    <row r="16" ht="28.35" customHeight="1">
+      <c r="B16" s="69" t="n"/>
+      <c r="C16" s="70" t="n"/>
+      <c r="K16" s="69" t="n"/>
+      <c r="L16" s="70" t="n"/>
+      <c r="R16" s="69" t="n"/>
+      <c r="S16" s="70" t="n"/>
+      <c r="AA16" s="69" t="n"/>
+      <c r="AB16" s="70" t="n"/>
+      <c r="AF16" s="12" t="n"/>
+      <c r="AG16" s="12" t="n"/>
+      <c r="AH16" s="12" t="n"/>
+      <c r="AI16" s="65" t="n"/>
+      <c r="AJ16" s="66" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="B17" s="69" t="n"/>
+      <c r="C17" s="70" t="n"/>
+      <c r="K17" s="69" t="n"/>
+      <c r="L17" s="70" t="n"/>
+      <c r="R17" s="69" t="n"/>
+      <c r="S17" s="70" t="n"/>
+      <c r="AA17" s="69" t="n"/>
+      <c r="AB17" s="70" t="n"/>
+      <c r="AF17" s="12" t="n"/>
+      <c r="AG17" s="12" t="n"/>
+      <c r="AH17" s="12" t="n"/>
+      <c r="AI17" s="36" t="inlineStr">
+        <is>
+          <t>Procedimental: Manipula las etiquetas básicas para la elaboración de paginas web</t>
+        </is>
+      </c>
+      <c r="AJ17" s="64" t="n"/>
+    </row>
+    <row r="18" ht="45.6" customHeight="1">
+      <c r="B18" s="69" t="n"/>
+      <c r="C18" s="70" t="n"/>
+      <c r="K18" s="69" t="n"/>
+      <c r="L18" s="70" t="n"/>
+      <c r="R18" s="69" t="n"/>
+      <c r="S18" s="70" t="n"/>
+      <c r="AA18" s="69" t="n"/>
+      <c r="AB18" s="70" t="n"/>
+      <c r="AF18" s="12" t="n"/>
+      <c r="AG18" s="12" t="n"/>
+      <c r="AH18" s="12" t="n"/>
+      <c r="AI18" s="65" t="n"/>
+      <c r="AJ18" s="66" t="n"/>
+    </row>
+    <row r="19" ht="27.4" customHeight="1">
+      <c r="B19" s="69" t="n"/>
+      <c r="C19" s="70" t="n"/>
+      <c r="K19" s="69" t="n"/>
+      <c r="L19" s="70" t="n"/>
+      <c r="R19" s="69" t="n"/>
+      <c r="S19" s="70" t="n"/>
+      <c r="AA19" s="69" t="n"/>
+      <c r="AB19" s="70" t="n"/>
+      <c r="AF19" s="12" t="n"/>
+      <c r="AG19" s="12" t="n"/>
+      <c r="AH19" s="12" t="n"/>
+      <c r="AI19" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actitudinal: Valora las etiquetas  básicas de html. </t>
+        </is>
+      </c>
+      <c r="AJ19" s="64" t="n"/>
+    </row>
+    <row r="20" ht="35.25" customHeight="1">
+      <c r="B20" s="69" t="n"/>
+      <c r="C20" s="65" t="n"/>
+      <c r="D20" s="61" t="n"/>
+      <c r="E20" s="61" t="n"/>
+      <c r="F20" s="61" t="n"/>
+      <c r="G20" s="61" t="n"/>
+      <c r="H20" s="61" t="n"/>
+      <c r="I20" s="61" t="n"/>
+      <c r="J20" s="61" t="n"/>
+      <c r="K20" s="66" t="n"/>
+      <c r="L20" s="65" t="n"/>
+      <c r="M20" s="61" t="n"/>
+      <c r="N20" s="61" t="n"/>
+      <c r="O20" s="61" t="n"/>
+      <c r="P20" s="61" t="n"/>
+      <c r="Q20" s="61" t="n"/>
+      <c r="R20" s="66" t="n"/>
+      <c r="S20" s="65" t="n"/>
+      <c r="T20" s="61" t="n"/>
+      <c r="U20" s="61" t="n"/>
+      <c r="V20" s="61" t="n"/>
+      <c r="W20" s="61" t="n"/>
+      <c r="X20" s="61" t="n"/>
+      <c r="Y20" s="61" t="n"/>
+      <c r="Z20" s="61" t="n"/>
+      <c r="AA20" s="66" t="n"/>
+      <c r="AB20" s="65" t="n"/>
+      <c r="AC20" s="61" t="n"/>
+      <c r="AD20" s="61" t="n"/>
+      <c r="AE20" s="61" t="n"/>
+      <c r="AF20" s="13" t="n"/>
+      <c r="AG20" s="13" t="n"/>
+      <c r="AH20" s="13" t="n"/>
+      <c r="AI20" s="65" t="n"/>
+      <c r="AJ20" s="66" t="n"/>
+    </row>
+    <row r="21" ht="18.75" customHeight="1">
+      <c r="B21" s="69" t="n"/>
+      <c r="C21" s="73" t="n"/>
+      <c r="D21" s="63" t="n"/>
+      <c r="E21" s="63" t="n"/>
+      <c r="F21" s="63" t="n"/>
+      <c r="G21" s="63" t="n"/>
+      <c r="H21" s="63" t="n"/>
+      <c r="I21" s="63" t="n"/>
+      <c r="J21" s="63" t="n"/>
+      <c r="K21" s="64" t="n"/>
+      <c r="L21" s="73" t="n"/>
+      <c r="M21" s="63" t="n"/>
+      <c r="N21" s="63" t="n"/>
+      <c r="O21" s="63" t="n"/>
+      <c r="P21" s="63" t="n"/>
+      <c r="Q21" s="63" t="n"/>
+      <c r="R21" s="64" t="n"/>
+      <c r="S21" s="73" t="n"/>
+      <c r="T21" s="63" t="n"/>
+      <c r="U21" s="63" t="n"/>
+      <c r="V21" s="63" t="n"/>
+      <c r="W21" s="63" t="n"/>
+      <c r="X21" s="63" t="n"/>
+      <c r="Y21" s="63" t="n"/>
+      <c r="Z21" s="63" t="n"/>
+      <c r="AA21" s="64" t="n"/>
+      <c r="AB21" s="73" t="n"/>
+      <c r="AC21" s="63" t="n"/>
+      <c r="AD21" s="63" t="n"/>
+      <c r="AE21" s="64" t="n"/>
+      <c r="AF21" s="12" t="n"/>
+      <c r="AG21" s="12" t="n"/>
+      <c r="AH21" s="12" t="n"/>
+      <c r="AI21" s="74" t="n"/>
+      <c r="AJ21" s="64" t="n"/>
+    </row>
+    <row r="22" ht="32.85" customHeight="1">
+      <c r="B22" s="69" t="n"/>
+      <c r="C22" s="70" t="n"/>
+      <c r="K22" s="69" t="n"/>
+      <c r="L22" s="70" t="n"/>
+      <c r="R22" s="69" t="n"/>
+      <c r="S22" s="70" t="n"/>
+      <c r="AA22" s="69" t="n"/>
+      <c r="AB22" s="70" t="n"/>
+      <c r="AE22" s="69" t="n"/>
+      <c r="AF22" s="12" t="n"/>
+      <c r="AG22" s="12" t="n"/>
+      <c r="AH22" s="12" t="n"/>
+      <c r="AI22" s="65" t="n"/>
+      <c r="AJ22" s="66" t="n"/>
+    </row>
+    <row r="23" ht="18.75" customHeight="1">
+      <c r="B23" s="69" t="n"/>
+      <c r="C23" s="70" t="n"/>
+      <c r="K23" s="69" t="n"/>
+      <c r="L23" s="70" t="n"/>
+      <c r="R23" s="69" t="n"/>
+      <c r="S23" s="70" t="n"/>
+      <c r="AA23" s="69" t="n"/>
+      <c r="AB23" s="70" t="n"/>
+      <c r="AE23" s="69" t="n"/>
+      <c r="AF23" s="12" t="n"/>
+      <c r="AG23" s="12" t="n"/>
+      <c r="AH23" s="12" t="n"/>
+      <c r="AI23" s="74" t="n"/>
+      <c r="AJ23" s="64" t="n"/>
+    </row>
+    <row r="24" ht="38.1" customHeight="1">
+      <c r="B24" s="69" t="n"/>
+      <c r="C24" s="70" t="n"/>
+      <c r="K24" s="69" t="n"/>
+      <c r="L24" s="70" t="n"/>
+      <c r="R24" s="69" t="n"/>
+      <c r="S24" s="70" t="n"/>
+      <c r="AA24" s="69" t="n"/>
+      <c r="AB24" s="70" t="n"/>
+      <c r="AE24" s="69" t="n"/>
+      <c r="AF24" s="12" t="n"/>
+      <c r="AG24" s="12" t="n"/>
+      <c r="AH24" s="12" t="n"/>
+      <c r="AI24" s="65" t="n"/>
+      <c r="AJ24" s="66" t="n"/>
+    </row>
+    <row r="25" ht="18.75" customHeight="1">
+      <c r="B25" s="69" t="n"/>
+      <c r="C25" s="70" t="n"/>
+      <c r="K25" s="69" t="n"/>
+      <c r="L25" s="70" t="n"/>
+      <c r="R25" s="69" t="n"/>
+      <c r="S25" s="70" t="n"/>
+      <c r="AA25" s="69" t="n"/>
+      <c r="AB25" s="70" t="n"/>
+      <c r="AE25" s="69" t="n"/>
+      <c r="AF25" s="12" t="n"/>
+      <c r="AG25" s="12" t="n"/>
+      <c r="AH25" s="12" t="n"/>
+      <c r="AI25" s="74" t="n"/>
+      <c r="AJ25" s="64" t="n"/>
+    </row>
+    <row r="26" ht="33.6" customHeight="1">
+      <c r="B26" s="69" t="n"/>
+      <c r="C26" s="70" t="n"/>
+      <c r="K26" s="69" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="R26" s="69" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="AA26" s="69" t="n"/>
+      <c r="AB26" s="70" t="n"/>
+      <c r="AE26" s="69" t="n"/>
+      <c r="AF26" s="12" t="n"/>
+      <c r="AG26" s="12" t="n"/>
+      <c r="AH26" s="12" t="n"/>
+      <c r="AI26" s="70" t="n"/>
+      <c r="AJ26" s="69" t="n"/>
+    </row>
+    <row r="27" ht="18.75" customHeight="1">
+      <c r="B27" s="69" t="n"/>
+      <c r="C27" s="65" t="n"/>
+      <c r="D27" s="61" t="n"/>
+      <c r="E27" s="61" t="n"/>
+      <c r="F27" s="61" t="n"/>
+      <c r="G27" s="61" t="n"/>
+      <c r="H27" s="61" t="n"/>
+      <c r="I27" s="61" t="n"/>
+      <c r="J27" s="61" t="n"/>
+      <c r="K27" s="66" t="n"/>
+      <c r="L27" s="65" t="n"/>
+      <c r="M27" s="61" t="n"/>
+      <c r="N27" s="61" t="n"/>
+      <c r="O27" s="61" t="n"/>
+      <c r="P27" s="61" t="n"/>
+      <c r="Q27" s="61" t="n"/>
+      <c r="R27" s="66" t="n"/>
+      <c r="S27" s="65" t="n"/>
+      <c r="T27" s="61" t="n"/>
+      <c r="U27" s="61" t="n"/>
+      <c r="V27" s="61" t="n"/>
+      <c r="W27" s="61" t="n"/>
+      <c r="X27" s="61" t="n"/>
+      <c r="Y27" s="61" t="n"/>
+      <c r="Z27" s="61" t="n"/>
+      <c r="AA27" s="66" t="n"/>
+      <c r="AB27" s="65" t="n"/>
+      <c r="AC27" s="61" t="n"/>
+      <c r="AD27" s="61" t="n"/>
+      <c r="AE27" s="66" t="n"/>
+      <c r="AF27" s="12" t="n"/>
+      <c r="AG27" s="12" t="n"/>
+      <c r="AH27" s="12" t="n"/>
+      <c r="AI27" s="65" t="n"/>
+      <c r="AJ27" s="66" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="B28" s="69" t="n"/>
+      <c r="C28" s="75" t="n"/>
+      <c r="D28" s="63" t="n"/>
+      <c r="E28" s="63" t="n"/>
+      <c r="F28" s="63" t="n"/>
+      <c r="G28" s="63" t="n"/>
+      <c r="H28" s="63" t="n"/>
+      <c r="I28" s="63" t="n"/>
+      <c r="J28" s="63" t="n"/>
+      <c r="K28" s="64" t="n"/>
+      <c r="L28" s="75" t="n"/>
+      <c r="M28" s="63" t="n"/>
+      <c r="N28" s="63" t="n"/>
+      <c r="O28" s="63" t="n"/>
+      <c r="P28" s="63" t="n"/>
+      <c r="Q28" s="63" t="n"/>
+      <c r="R28" s="64" t="n"/>
+      <c r="S28" s="75" t="n"/>
+      <c r="T28" s="63" t="n"/>
+      <c r="U28" s="63" t="n"/>
+      <c r="V28" s="63" t="n"/>
+      <c r="W28" s="63" t="n"/>
+      <c r="X28" s="63" t="n"/>
+      <c r="Y28" s="63" t="n"/>
+      <c r="Z28" s="63" t="n"/>
+      <c r="AA28" s="64" t="n"/>
+      <c r="AB28" s="75" t="n"/>
+      <c r="AC28" s="63" t="n"/>
+      <c r="AD28" s="63" t="n"/>
+      <c r="AE28" s="64" t="n"/>
+      <c r="AF28" s="14" t="n"/>
+      <c r="AG28" s="14" t="n"/>
+      <c r="AH28" s="14" t="n"/>
+      <c r="AI28" s="75" t="n"/>
+      <c r="AJ28" s="64" t="n"/>
+    </row>
+    <row r="29" ht="30.6" customHeight="1">
+      <c r="B29" s="69" t="n"/>
+      <c r="C29" s="70" t="n"/>
+      <c r="K29" s="69" t="n"/>
+      <c r="L29" s="70" t="n"/>
+      <c r="R29" s="69" t="n"/>
+      <c r="S29" s="70" t="n"/>
+      <c r="AA29" s="69" t="n"/>
+      <c r="AB29" s="70" t="n"/>
+      <c r="AE29" s="69" t="n"/>
+      <c r="AF29" s="14" t="n"/>
+      <c r="AG29" s="14" t="n"/>
+      <c r="AH29" s="14" t="n"/>
+      <c r="AI29" s="65" t="n"/>
+      <c r="AJ29" s="66" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="B30" s="69" t="n"/>
+      <c r="C30" s="70" t="n"/>
+      <c r="K30" s="69" t="n"/>
+      <c r="L30" s="70" t="n"/>
+      <c r="R30" s="69" t="n"/>
+      <c r="S30" s="70" t="n"/>
+      <c r="AA30" s="69" t="n"/>
+      <c r="AB30" s="70" t="n"/>
+      <c r="AE30" s="69" t="n"/>
+      <c r="AF30" s="14" t="n"/>
+      <c r="AG30" s="14" t="n"/>
+      <c r="AH30" s="14" t="n"/>
+      <c r="AI30" s="75" t="n"/>
+      <c r="AJ30" s="64" t="n"/>
+    </row>
+    <row r="31" ht="41.45" customHeight="1">
+      <c r="B31" s="69" t="n"/>
+      <c r="C31" s="70" t="n"/>
+      <c r="K31" s="69" t="n"/>
+      <c r="L31" s="70" t="n"/>
+      <c r="R31" s="69" t="n"/>
+      <c r="S31" s="70" t="n"/>
+      <c r="AA31" s="69" t="n"/>
+      <c r="AB31" s="70" t="n"/>
+      <c r="AE31" s="69" t="n"/>
+      <c r="AF31" s="14" t="n"/>
+      <c r="AG31" s="14" t="n"/>
+      <c r="AH31" s="14" t="n"/>
+      <c r="AI31" s="65" t="n"/>
+      <c r="AJ31" s="66" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="B32" s="69" t="n"/>
+      <c r="C32" s="70" t="n"/>
+      <c r="K32" s="69" t="n"/>
+      <c r="L32" s="70" t="n"/>
+      <c r="R32" s="69" t="n"/>
+      <c r="S32" s="70" t="n"/>
+      <c r="AA32" s="69" t="n"/>
+      <c r="AB32" s="70" t="n"/>
+      <c r="AE32" s="69" t="n"/>
+      <c r="AF32" s="14" t="n"/>
+      <c r="AG32" s="14" t="n"/>
+      <c r="AH32" s="14" t="n"/>
+      <c r="AI32" s="75" t="n"/>
+      <c r="AJ32" s="64" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="69" t="n"/>
+      <c r="C33" s="70" t="n"/>
+      <c r="K33" s="69" t="n"/>
+      <c r="L33" s="70" t="n"/>
+      <c r="R33" s="69" t="n"/>
+      <c r="S33" s="70" t="n"/>
+      <c r="AA33" s="69" t="n"/>
+      <c r="AB33" s="70" t="n"/>
+      <c r="AE33" s="69" t="n"/>
+      <c r="AF33" s="14" t="n"/>
+      <c r="AG33" s="14" t="n"/>
+      <c r="AH33" s="14" t="n"/>
+      <c r="AI33" s="70" t="n"/>
+      <c r="AJ33" s="69" t="n"/>
+    </row>
+    <row r="34" ht="35.65" customHeight="1">
+      <c r="B34" s="69" t="n"/>
+      <c r="C34" s="65" t="n"/>
+      <c r="D34" s="61" t="n"/>
+      <c r="E34" s="61" t="n"/>
+      <c r="F34" s="61" t="n"/>
+      <c r="G34" s="61" t="n"/>
+      <c r="H34" s="61" t="n"/>
+      <c r="I34" s="61" t="n"/>
+      <c r="J34" s="61" t="n"/>
+      <c r="K34" s="66" t="n"/>
+      <c r="L34" s="65" t="n"/>
+      <c r="M34" s="61" t="n"/>
+      <c r="N34" s="61" t="n"/>
+      <c r="O34" s="61" t="n"/>
+      <c r="P34" s="61" t="n"/>
+      <c r="Q34" s="61" t="n"/>
+      <c r="R34" s="66" t="n"/>
+      <c r="S34" s="65" t="n"/>
+      <c r="T34" s="61" t="n"/>
+      <c r="U34" s="61" t="n"/>
+      <c r="V34" s="61" t="n"/>
+      <c r="W34" s="61" t="n"/>
+      <c r="X34" s="61" t="n"/>
+      <c r="Y34" s="61" t="n"/>
+      <c r="Z34" s="61" t="n"/>
+      <c r="AA34" s="66" t="n"/>
+      <c r="AB34" s="65" t="n"/>
+      <c r="AC34" s="61" t="n"/>
+      <c r="AD34" s="61" t="n"/>
+      <c r="AE34" s="66" t="n"/>
+      <c r="AF34" s="14" t="n"/>
+      <c r="AG34" s="14" t="n"/>
+      <c r="AH34" s="14" t="n"/>
+      <c r="AI34" s="65" t="n"/>
+      <c r="AJ34" s="66" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="B35" s="69" t="n"/>
+      <c r="C35" s="73" t="n"/>
+      <c r="D35" s="63" t="n"/>
+      <c r="E35" s="63" t="n"/>
+      <c r="F35" s="63" t="n"/>
+      <c r="G35" s="63" t="n"/>
+      <c r="H35" s="63" t="n"/>
+      <c r="I35" s="63" t="n"/>
+      <c r="J35" s="63" t="n"/>
+      <c r="K35" s="64" t="n"/>
+      <c r="L35" s="73" t="n"/>
+      <c r="M35" s="63" t="n"/>
+      <c r="N35" s="63" t="n"/>
+      <c r="O35" s="63" t="n"/>
+      <c r="P35" s="63" t="n"/>
+      <c r="Q35" s="63" t="n"/>
+      <c r="R35" s="64" t="n"/>
+      <c r="S35" s="73" t="n"/>
+      <c r="T35" s="63" t="n"/>
+      <c r="U35" s="63" t="n"/>
+      <c r="V35" s="63" t="n"/>
+      <c r="W35" s="63" t="n"/>
+      <c r="X35" s="63" t="n"/>
+      <c r="Y35" s="63" t="n"/>
+      <c r="Z35" s="63" t="n"/>
+      <c r="AA35" s="64" t="n"/>
+      <c r="AB35" s="73" t="n"/>
+      <c r="AC35" s="63" t="n"/>
+      <c r="AD35" s="63" t="n"/>
+      <c r="AE35" s="64" t="n"/>
+      <c r="AF35" s="15" t="n"/>
+      <c r="AG35" s="15" t="n"/>
+      <c r="AH35" s="15" t="n"/>
+      <c r="AI35" s="73" t="n"/>
+      <c r="AJ35" s="64" t="n"/>
+    </row>
+    <row r="36" ht="31.5" customHeight="1">
+      <c r="B36" s="69" t="n"/>
+      <c r="C36" s="70" t="n"/>
+      <c r="K36" s="69" t="n"/>
+      <c r="L36" s="70" t="n"/>
+      <c r="R36" s="69" t="n"/>
+      <c r="S36" s="70" t="n"/>
+      <c r="AA36" s="69" t="n"/>
+      <c r="AB36" s="70" t="n"/>
+      <c r="AE36" s="69" t="n"/>
+      <c r="AF36" s="15" t="n"/>
+      <c r="AG36" s="15" t="n"/>
+      <c r="AH36" s="15" t="n"/>
+      <c r="AI36" s="65" t="n"/>
+      <c r="AJ36" s="66" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="69" t="n"/>
+      <c r="C37" s="70" t="n"/>
+      <c r="K37" s="69" t="n"/>
+      <c r="L37" s="70" t="n"/>
+      <c r="R37" s="69" t="n"/>
+      <c r="S37" s="70" t="n"/>
+      <c r="AA37" s="69" t="n"/>
+      <c r="AB37" s="70" t="n"/>
+      <c r="AE37" s="69" t="n"/>
+      <c r="AF37" s="15" t="n"/>
+      <c r="AG37" s="15" t="n"/>
+      <c r="AH37" s="15" t="n"/>
+      <c r="AI37" s="73" t="n"/>
+      <c r="AJ37" s="64" t="n"/>
+    </row>
+    <row r="38" ht="31.5" customHeight="1">
+      <c r="B38" s="69" t="n"/>
+      <c r="C38" s="70" t="n"/>
+      <c r="K38" s="69" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="R38" s="69" t="n"/>
+      <c r="S38" s="70" t="n"/>
+      <c r="AA38" s="69" t="n"/>
+      <c r="AB38" s="70" t="n"/>
+      <c r="AE38" s="69" t="n"/>
+      <c r="AF38" s="15" t="n"/>
+      <c r="AG38" s="15" t="n"/>
+      <c r="AH38" s="15" t="n"/>
+      <c r="AI38" s="65" t="n"/>
+      <c r="AJ38" s="66" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="B39" s="69" t="n"/>
+      <c r="C39" s="70" t="n"/>
+      <c r="K39" s="69" t="n"/>
+      <c r="L39" s="70" t="n"/>
+      <c r="R39" s="69" t="n"/>
+      <c r="S39" s="70" t="n"/>
+      <c r="AA39" s="69" t="n"/>
+      <c r="AB39" s="70" t="n"/>
+      <c r="AE39" s="69" t="n"/>
+      <c r="AF39" s="15" t="n"/>
+      <c r="AG39" s="15" t="n"/>
+      <c r="AH39" s="15" t="n"/>
+      <c r="AI39" s="73" t="n"/>
+      <c r="AJ39" s="64" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="69" t="n"/>
+      <c r="C40" s="70" t="n"/>
+      <c r="K40" s="69" t="n"/>
+      <c r="L40" s="70" t="n"/>
+      <c r="R40" s="69" t="n"/>
+      <c r="S40" s="70" t="n"/>
+      <c r="AA40" s="69" t="n"/>
+      <c r="AB40" s="70" t="n"/>
+      <c r="AE40" s="69" t="n"/>
+      <c r="AF40" s="15" t="n"/>
+      <c r="AG40" s="15" t="n"/>
+      <c r="AH40" s="15" t="n"/>
+      <c r="AI40" s="70" t="n"/>
+      <c r="AJ40" s="69" t="n"/>
+    </row>
+    <row r="41" ht="25.7" customHeight="1">
+      <c r="B41" s="69" t="n"/>
+      <c r="C41" s="65" t="n"/>
+      <c r="D41" s="61" t="n"/>
+      <c r="E41" s="61" t="n"/>
+      <c r="F41" s="61" t="n"/>
+      <c r="G41" s="61" t="n"/>
+      <c r="H41" s="61" t="n"/>
+      <c r="I41" s="61" t="n"/>
+      <c r="J41" s="61" t="n"/>
+      <c r="K41" s="66" t="n"/>
+      <c r="L41" s="65" t="n"/>
+      <c r="M41" s="61" t="n"/>
+      <c r="N41" s="61" t="n"/>
+      <c r="O41" s="61" t="n"/>
+      <c r="P41" s="61" t="n"/>
+      <c r="Q41" s="61" t="n"/>
+      <c r="R41" s="66" t="n"/>
+      <c r="S41" s="65" t="n"/>
+      <c r="T41" s="61" t="n"/>
+      <c r="U41" s="61" t="n"/>
+      <c r="V41" s="61" t="n"/>
+      <c r="W41" s="61" t="n"/>
+      <c r="X41" s="61" t="n"/>
+      <c r="Y41" s="61" t="n"/>
+      <c r="Z41" s="61" t="n"/>
+      <c r="AA41" s="66" t="n"/>
+      <c r="AB41" s="65" t="n"/>
+      <c r="AC41" s="61" t="n"/>
+      <c r="AD41" s="61" t="n"/>
+      <c r="AE41" s="66" t="n"/>
+      <c r="AF41" s="15" t="n"/>
+      <c r="AG41" s="15" t="n"/>
+      <c r="AH41" s="15" t="n"/>
+      <c r="AI41" s="65" t="n"/>
+      <c r="AJ41" s="66" t="n"/>
+    </row>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+  </sheetData>
+  <mergeCells count="45">
+    <mergeCell ref="AI39:AJ41"/>
+    <mergeCell ref="L28:R34"/>
+    <mergeCell ref="S15:AA20"/>
+    <mergeCell ref="C2:AJ2"/>
+    <mergeCell ref="AI35:AJ36"/>
+    <mergeCell ref="S21:AA27"/>
+    <mergeCell ref="M9:R10"/>
+    <mergeCell ref="B9:L10"/>
+    <mergeCell ref="L35:R41"/>
+    <mergeCell ref="W9:AJ10"/>
+    <mergeCell ref="AI21:AJ22"/>
+    <mergeCell ref="B12:B41"/>
+    <mergeCell ref="AI17:AJ18"/>
+    <mergeCell ref="B7:V8"/>
+    <mergeCell ref="C35:K41"/>
+    <mergeCell ref="AI37:AJ38"/>
+    <mergeCell ref="C12:K14"/>
+    <mergeCell ref="S9:V10"/>
+    <mergeCell ref="L15:R20"/>
+    <mergeCell ref="L21:R27"/>
+    <mergeCell ref="AB28:AE34"/>
+    <mergeCell ref="C3:AJ3"/>
+    <mergeCell ref="AB14:AE14"/>
+    <mergeCell ref="C15:K20"/>
+    <mergeCell ref="C21:K27"/>
+    <mergeCell ref="B5:AJ6"/>
+    <mergeCell ref="AB12:AJ13"/>
+    <mergeCell ref="S28:AA34"/>
+    <mergeCell ref="AI23:AJ24"/>
+    <mergeCell ref="AI25:AJ27"/>
+    <mergeCell ref="AI19:AJ20"/>
+    <mergeCell ref="AB21:AE27"/>
+    <mergeCell ref="AI32:AJ34"/>
+    <mergeCell ref="S12:AA14"/>
+    <mergeCell ref="AI15:AJ16"/>
+    <mergeCell ref="C4:AJ4"/>
+    <mergeCell ref="AI28:AJ29"/>
+    <mergeCell ref="L12:R14"/>
+    <mergeCell ref="AB35:AE41"/>
+    <mergeCell ref="S35:AA41"/>
+    <mergeCell ref="AI14:AJ14"/>
+    <mergeCell ref="AI30:AJ31"/>
+    <mergeCell ref="W7:AJ8"/>
+    <mergeCell ref="AB15:AE20"/>
+    <mergeCell ref="C28:K34"/>
+  </mergeCells>
+  <pageMargins left="1.29930555555556" right="0.905555555555556" top="0.551388888888889" bottom="0.354166666666667" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="5" scale="70" horizontalDpi="300" verticalDpi="300"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>